--- a/files/九龙-将军澳-凯柏峰 I.xlsx
+++ b/files/九龙-将军澳-凯柏峰 I.xlsx
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -30897,7 +30897,7 @@
           <t>C | 410呎 (2房)
 $734万
 $17,896/呎
-(25年-09月)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">

--- a/files/九龙-将军澳-凯柏峰 I.xlsx
+++ b/files/九龙-将军澳-凯柏峰 I.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -146,8 +172,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,19 +220,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,13 +238,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -27923,148 +27961,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯柏峰 I - 1A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>320 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>319 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 897呎 (3房)
-$1,850万
+$1850万
 $20,624/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 426呎 (2房)
 $767万
@@ -28072,7 +28110,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $571万
@@ -28080,7 +28118,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 453呎 (2房)
 $804万
@@ -28088,7 +28126,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 807呎 (3房)
 招标单位
@@ -28096,15 +28134,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $769万
@@ -28112,15 +28150,15 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,370万
+$1370万
 $19,000/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $853万
@@ -28128,7 +28166,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $668万
@@ -28136,7 +28174,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $828万
@@ -28144,7 +28182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 460呎 (2房)
 $801万
@@ -28152,7 +28190,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $802万
@@ -28161,13 +28199,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $916万
@@ -28175,15 +28213,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,355万
+$1355万
 $18,792/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $809万
@@ -28191,7 +28229,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $551万
@@ -28199,7 +28237,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $872万
@@ -28207,7 +28245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $784万
@@ -28215,7 +28253,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $793万
@@ -28224,13 +28262,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $768万
@@ -28238,15 +28276,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,381万
+$1381万
 $19,151/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $851万
@@ -28254,7 +28292,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $551万
@@ -28262,7 +28300,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -28270,7 +28308,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $782万
@@ -28278,7 +28316,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $791万
@@ -28287,13 +28325,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $768万
@@ -28301,15 +28339,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,436万
+$1436万
 $19,920/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $808万
@@ -28317,7 +28355,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $666万
@@ -28325,7 +28363,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $871万
@@ -28333,7 +28371,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $782万
@@ -28341,7 +28379,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $791万
@@ -28350,13 +28388,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $766万
@@ -28364,15 +28402,15 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,354万
+$1354万
 $18,782/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $850万
@@ -28380,7 +28418,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $665万
@@ -28388,7 +28426,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $869万
@@ -28396,7 +28434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $771万
@@ -28404,7 +28442,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $772万
@@ -28413,13 +28451,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $866万
@@ -28427,15 +28465,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,353万
+$1353万
 $18,763/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $761万
@@ -28443,7 +28481,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $700万
@@ -28451,7 +28489,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $868万
@@ -28459,7 +28497,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $770万
@@ -28467,7 +28505,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $771万
@@ -28476,13 +28514,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $844万
@@ -28490,15 +28528,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,372万
+$1372万
 $19,026/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $848万
@@ -28506,7 +28544,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $699万
@@ -28514,7 +28552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -28522,7 +28560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $768万
@@ -28530,7 +28568,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $769万
@@ -28539,13 +28577,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $843万
@@ -28553,15 +28591,15 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,447万
+$1447万
 $20,072/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $847万
@@ -28569,7 +28607,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $550万
@@ -28577,7 +28615,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $867万
@@ -28585,7 +28623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $767万
@@ -28593,7 +28631,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $768万
@@ -28602,13 +28640,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $818万
@@ -28616,15 +28654,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,346万
+$1346万
 $18,662/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $846万
@@ -28632,7 +28670,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $698万
@@ -28640,7 +28678,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $866万
@@ -28648,7 +28686,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $757万
@@ -28656,7 +28694,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $766万
@@ -28665,13 +28703,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $909万
@@ -28679,15 +28717,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,351万
+$1351万
 $18,735/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $845万
@@ -28695,7 +28733,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $662万
@@ -28703,7 +28741,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $807万
@@ -28711,7 +28749,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $927万
@@ -28719,7 +28757,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $765万
@@ -28728,13 +28766,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $800万
@@ -28742,15 +28780,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,349万
+$1349万
 $18,716/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $844万
@@ -28758,7 +28796,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $549万
@@ -28766,7 +28804,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $820万
@@ -28774,7 +28812,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $878万
@@ -28782,7 +28820,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $875万
@@ -28791,13 +28829,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $907万
@@ -28805,15 +28843,15 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,466万
+$1466万
 $20,337/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $801万
@@ -28821,7 +28859,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $696万
@@ -28829,7 +28867,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $821万
@@ -28837,7 +28875,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $923万
@@ -28845,7 +28883,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $817万
@@ -28854,13 +28892,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $906万
@@ -28868,15 +28906,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,396万
+$1396万
 $19,358/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $810万
@@ -28884,7 +28922,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $695万
@@ -28892,7 +28930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $862万
@@ -28900,7 +28938,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $877万
@@ -28908,7 +28946,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $920万
@@ -28917,13 +28955,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $905万
@@ -28931,15 +28969,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,421万
+$1421万
 $19,706/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $755万
@@ -28947,7 +28985,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $659万
@@ -28955,7 +28993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $818万
@@ -28963,7 +29001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $920万
@@ -28971,7 +29009,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $870万
@@ -28980,13 +29018,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $873万
@@ -28994,15 +29032,15 @@
 (22年-07月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,344万
+$1344万
 $18,641/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $808万
@@ -29010,7 +29048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $658万
@@ -29018,7 +29056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $860万
@@ -29026,7 +29064,7 @@
 (22年-07月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 460呎 (2房)
 $800万
@@ -29034,7 +29072,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $814万
@@ -29043,13 +29081,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $804万
@@ -29057,15 +29095,15 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,336万
+$1336万
 $18,531/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $793万
@@ -29073,7 +29111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $607万
@@ -29081,7 +29119,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $857万
@@ -29089,7 +29127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $870万
@@ -29097,7 +29135,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $842万
@@ -29106,13 +29144,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $803万
@@ -29120,15 +29158,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,335万
+$1335万
 $18,512/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $835万
@@ -29136,7 +29174,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $692万
@@ -29144,7 +29182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $813万
@@ -29152,7 +29190,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $914万
@@ -29160,7 +29198,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $842万
@@ -29169,13 +29207,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $901万
@@ -29183,15 +29221,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,370万
+$1370万
 $19,003/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $834万
@@ -29199,7 +29237,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $656万
@@ -29207,7 +29245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $812万
@@ -29215,7 +29253,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $775万
@@ -29223,7 +29261,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $879万
@@ -29232,13 +29270,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $900万
@@ -29246,15 +29284,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,369万
+$1369万
 $18,985/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $833万
@@ -29262,7 +29300,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $656万
@@ -29270,7 +29308,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $855万
@@ -29278,7 +29316,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $864万
@@ -29286,7 +29324,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $861万
@@ -29295,13 +29333,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $899万
@@ -29309,15 +29347,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,320万
+$1320万
 $18,305/呎
 (22年-07月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $789万
@@ -29325,7 +29363,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $690万
@@ -29333,7 +29371,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $853万
@@ -29341,7 +29379,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $855万
@@ -29349,7 +29387,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $867万
@@ -29358,13 +29396,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $784万
@@ -29372,15 +29410,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,297万
+$1297万
 $17,984/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $742万
@@ -29388,7 +29426,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $690万
@@ -29396,7 +29434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $853万
@@ -29404,7 +29442,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $901万
@@ -29412,7 +29450,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $898万
@@ -29421,13 +29459,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $800万
@@ -29435,15 +29473,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,361万
+$1361万
 $18,871/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $748万
@@ -29451,7 +29489,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $603万
@@ -29459,7 +29497,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $819万
@@ -29467,7 +29505,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $891万
@@ -29475,7 +29513,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $843万
@@ -29484,13 +29522,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $784万
@@ -29498,15 +29536,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,358万
+$1358万
 $18,833/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $784万
@@ -29514,7 +29552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $685万
@@ -29522,7 +29560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $805万
@@ -29530,7 +29568,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $888万
@@ -29538,7 +29576,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $840万
@@ -29547,13 +29585,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $891万
@@ -29561,15 +29599,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,355万
+$1355万
 $18,796/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $783万
@@ -29577,7 +29615,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $684万
@@ -29585,7 +29623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $846万
@@ -29593,7 +29631,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $886万
@@ -29601,7 +29639,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $838万
@@ -29610,13 +29648,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $890万
@@ -29624,15 +29662,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,352万
+$1352万
 $18,758/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $746万
@@ -29640,7 +29678,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $648万
@@ -29648,7 +29686,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $816万
@@ -29656,7 +29694,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $834万
@@ -29664,7 +29702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $835万
@@ -29673,13 +29711,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $888万
@@ -29687,15 +29725,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,350万
+$1350万
 $18,720/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $822万
@@ -29703,7 +29741,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $643万
@@ -29711,7 +29749,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $843万
@@ -29719,7 +29757,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 460呎 (2房)
 $876万
@@ -29727,7 +29765,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $877万
@@ -29736,13 +29774,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $886万
@@ -29750,15 +29788,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,301万
+$1301万
 $18,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $820万
@@ -29766,7 +29804,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $532万
@@ -29774,7 +29812,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $841万
@@ -29782,7 +29820,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $844万
@@ -29790,7 +29828,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $830万
@@ -29799,13 +29837,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $839万
@@ -29813,15 +29851,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,344万
+$1344万
 $18,645/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $818万
@@ -29829,7 +29867,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $652万
@@ -29837,7 +29875,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $840万
@@ -29845,7 +29883,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $871万
@@ -29853,7 +29891,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $872万
@@ -29862,13 +29900,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $883万
@@ -29876,15 +29914,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,342万
+$1342万
 $18,609/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $735万
@@ -29892,7 +29930,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $531万
@@ -29900,7 +29938,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $799万
@@ -29908,7 +29946,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $868万
@@ -29916,7 +29954,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $869万
@@ -29925,13 +29963,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $838万
@@ -29939,15 +29977,15 @@
 (22年-07月)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,342万
+$1342万
 $18,609/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $775万
@@ -29955,7 +29993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $674万
@@ -29963,7 +30001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $795万
@@ -29971,7 +30009,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $824万
@@ -29979,7 +30017,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $869万
@@ -29988,13 +30026,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $834万
@@ -30002,15 +30040,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,336万
+$1336万
 $18,535/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $813万
@@ -30018,7 +30056,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $671万
@@ -30026,7 +30064,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $835万
@@ -30034,7 +30072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $859万
@@ -30042,7 +30080,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $860万
@@ -30051,13 +30089,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $877万
@@ -30065,15 +30103,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,266万
+$1266万
 $17,557/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $812万
@@ -30081,7 +30119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $670万
@@ -30089,7 +30127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $833万
@@ -30097,7 +30135,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $813万
@@ -30105,7 +30143,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $857万
@@ -30114,13 +30152,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $876万
@@ -30128,15 +30166,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,331万
+$1331万
 $18,460/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $810万
@@ -30144,7 +30182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $669万
@@ -30152,7 +30190,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $831万
@@ -30160,7 +30198,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $854万
@@ -30168,7 +30206,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $855万
@@ -30177,13 +30215,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $829万
@@ -30191,15 +30229,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,261万
+$1261万
 $17,487/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $809万
@@ -30207,7 +30245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $667万
@@ -30215,7 +30253,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $776万
@@ -30223,7 +30261,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $808万
@@ -30231,7 +30269,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $852万
@@ -30240,13 +30278,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $798万
@@ -30254,15 +30292,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,258万
+$1258万
 $17,452/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $732万
@@ -30270,7 +30308,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $666万
@@ -30278,7 +30316,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $828万
@@ -30286,7 +30324,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $805万
@@ -30294,7 +30332,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $850万
@@ -30303,13 +30341,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $826万
@@ -30317,15 +30355,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,310万
+$1310万
 $18,168/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $805万
@@ -30333,7 +30371,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $527万
@@ -30341,7 +30379,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $788万
@@ -30349,7 +30387,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $846万
@@ -30357,7 +30395,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H42" s="16" t="inlineStr">
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $847万
@@ -30366,13 +30404,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $869万
@@ -30380,15 +30418,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,241万
+$1241万
 $17,211/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $804万
@@ -30396,7 +30434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $663万
@@ -30404,7 +30442,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $825万
@@ -30412,7 +30450,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $843万
@@ -30420,7 +30458,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $785万
@@ -30429,13 +30467,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $867万
@@ -30443,15 +30481,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,238万
+$1238万
 $17,176/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $802万
@@ -30459,7 +30497,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $662万
@@ -30467,7 +30505,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $823万
@@ -30475,7 +30513,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $841万
@@ -30483,7 +30521,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H44" s="16" t="inlineStr">
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $886万
@@ -30492,13 +30530,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $867万
@@ -30506,15 +30544,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,261万
+$1261万
 $17,483/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $802万
@@ -30522,7 +30560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $628万
@@ -30530,7 +30568,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $781万
@@ -30538,7 +30576,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $841万
@@ -30546,7 +30584,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $842万
@@ -30555,13 +30593,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $820万
@@ -30569,15 +30607,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,299万
+$1299万
 $18,023/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $799万
@@ -30585,7 +30623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $659万
@@ -30593,7 +30631,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $767万
@@ -30601,7 +30639,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $836万
@@ -30609,7 +30647,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $837万
@@ -30618,13 +30656,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $862万
@@ -30632,15 +30670,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,297万
+$1297万
 $17,988/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $797万
@@ -30648,7 +30686,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $658万
@@ -30656,7 +30694,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $818万
@@ -30664,7 +30702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $833万
@@ -30672,7 +30710,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H47" s="16" t="inlineStr">
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $835万
@@ -30681,13 +30719,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $860万
@@ -30695,15 +30733,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,228万
+$1228万
 $17,039/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $755万
@@ -30711,7 +30749,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $657万
@@ -30719,7 +30757,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $816万
@@ -30727,7 +30765,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $749万
@@ -30735,7 +30773,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr">
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $790万
@@ -30744,13 +30782,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $805万
@@ -30758,15 +30796,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,248万
+$1248万
 $17,309/呎
 (22年-06月)</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $767万
@@ -30774,7 +30812,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $655万
@@ -30782,7 +30820,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $766万
@@ -30790,7 +30828,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $828万
@@ -30798,7 +30836,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H49" s="16" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $830万
@@ -30807,13 +30845,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>A | 448呎 (2房)
 $855万
@@ -30821,15 +30859,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>B | 721呎 (3房)
-$1,287万
+$1287万
 $17,845/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
 $736万
@@ -30837,7 +30875,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>D | 329呎 (1房)
 $653万
@@ -30845,7 +30883,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>E | 455呎 (2房)
 $812万
@@ -30853,7 +30891,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $823万
@@ -30861,7 +30899,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="H49" s="20" t="inlineStr">
         <is>
           <t>G | 455呎 (2房)
 $825万
@@ -30870,13 +30908,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>A | 410呎 (2房)
 $740万
@@ -30884,15 +30922,15 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>B | 680呎 (3房)
-$1,343万
+$1343万
 $19,749/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>C | 410呎 (2房)
 $734万
@@ -30900,7 +30938,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>D | 291呎 (1房)
 $490万
@@ -30908,7 +30946,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>E | 417呎 (2房)
 $707万
@@ -30916,7 +30954,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>F | 459呎 (2房)
 $735万
@@ -30924,7 +30962,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H50" s="20" t="inlineStr">
         <is>
           <t>G | 418呎 (2房)
 $756万
@@ -30935,7 +30973,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -30948,160 +30986,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>凯柏峰 I - 1B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>272 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>270 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>62/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 893呎 (3房)
-$1,797万
+$1797万
 $20,122/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 871呎 (3房)
-$1,731万
+$1731万
 $19,873/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>61/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $749万
@@ -31109,7 +31147,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $542万
@@ -31117,7 +31155,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $891万
@@ -31125,15 +31163,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,015万
+$1015万
 $18,100/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $573万
@@ -31141,7 +31179,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $597万
@@ -31150,13 +31188,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>60/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $756万
@@ -31164,7 +31202,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $541万
@@ -31172,7 +31210,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $874万
@@ -31180,15 +31218,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,013万
+$1013万
 $18,062/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $572万
@@ -31196,7 +31234,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $584万
@@ -31205,13 +31243,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>59/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $755万
@@ -31219,7 +31257,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $541万
@@ -31227,7 +31265,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $889万
@@ -31235,7 +31273,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $981万
@@ -31243,7 +31281,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $571万
@@ -31251,7 +31289,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $583万
@@ -31260,13 +31298,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>58/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $770万
@@ -31274,7 +31312,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $541万
@@ -31282,7 +31320,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $920万
@@ -31290,15 +31328,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,021万
+$1021万
 $18,203/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $570万
@@ -31306,7 +31344,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $594万
@@ -31315,13 +31353,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>57/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $746万
@@ -31329,7 +31367,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $540万
@@ -31337,7 +31375,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $918万
@@ -31345,7 +31383,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $967万
@@ -31353,7 +31391,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $569万
@@ -31361,7 +31399,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $592万
@@ -31370,13 +31408,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>56/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $745万
@@ -31384,7 +31422,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $539万
@@ -31392,7 +31430,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $871万
@@ -31400,15 +31438,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,147万
+$1147万
 $20,439/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $568万
@@ -31416,7 +31454,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $591万
@@ -31425,13 +31463,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>55/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $745万
@@ -31439,7 +31477,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $538万
@@ -31447,7 +31485,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $916万
@@ -31455,15 +31493,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,086万
+$1086万
 $19,360/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $567万
@@ -31471,7 +31509,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $578万
@@ -31480,13 +31518,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>53/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $744万
@@ -31494,7 +31532,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $538万
@@ -31502,7 +31540,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $869万
@@ -31510,15 +31548,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,142万
+$1142万
 $20,358/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $566万
@@ -31526,7 +31564,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $577万
@@ -31535,13 +31573,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>52/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $921万
@@ -31549,7 +31587,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $537万
@@ -31557,7 +31595,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $868万
@@ -31565,15 +31603,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,041万
+$1041万
 $18,563/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $565万
@@ -31581,7 +31619,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $570万
@@ -31590,13 +31628,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>51/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $873万
@@ -31604,7 +31642,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $537万
@@ -31612,7 +31650,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $867万
@@ -31620,15 +31658,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,138万
+$1138万
 $20,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $564万
@@ -31636,7 +31674,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $575万
@@ -31645,13 +31683,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>50/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $919万
@@ -31659,7 +31697,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $536万
@@ -31667,7 +31705,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $864万
@@ -31675,15 +31713,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,135万
+$1135万
 $20,235/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $564万
@@ -31691,7 +31729,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $717万
@@ -31700,13 +31738,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>49/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $918万
@@ -31714,7 +31752,7 @@
 (22年-07月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $536万
@@ -31722,7 +31760,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $879万
@@ -31730,15 +31768,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,133万
+$1133万
 $20,196/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $563万
@@ -31746,7 +31784,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $572万
@@ -31755,13 +31793,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>48/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $805万
@@ -31769,7 +31807,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $536万
@@ -31777,7 +31815,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $863万
@@ -31785,15 +31823,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,133万
+$1133万
 $20,196/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $562万
@@ -31801,7 +31839,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $572万
@@ -31810,13 +31848,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>47/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $916万
@@ -31824,7 +31862,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $535万
@@ -31832,7 +31870,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $908万
@@ -31840,15 +31878,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,128万
+$1128万
 $20,115/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $560万
@@ -31856,7 +31894,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $570万
@@ -31865,13 +31903,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>46/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $869万
@@ -31879,7 +31917,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $534万
@@ -31887,7 +31925,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $907万
@@ -31895,7 +31933,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $997万
@@ -31903,7 +31941,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $559万
@@ -31911,7 +31949,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $563万
@@ -31920,13 +31958,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $868万
@@ -31934,7 +31972,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $705万
@@ -31942,7 +31980,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $860万
@@ -31950,15 +31988,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,124万
+$1124万
 $20,035/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $558万
@@ -31966,7 +32004,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $562万
@@ -31975,13 +32013,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $913万
@@ -31989,7 +32027,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $742万
@@ -31997,7 +32035,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $859万
@@ -32005,15 +32043,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,122万
+$1122万
 $19,995/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $558万
@@ -32021,7 +32059,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $755万
@@ -32030,13 +32068,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $866万
@@ -32044,7 +32082,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $704万
@@ -32052,7 +32090,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $858万
@@ -32060,15 +32098,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,059万
+$1059万
 $18,879/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $557万
@@ -32076,7 +32114,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $744万
@@ -32085,13 +32123,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $912万
@@ -32099,7 +32137,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $741万
@@ -32107,7 +32145,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $857万
@@ -32115,15 +32153,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,117万
+$1117万
 $19,915/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $556万
@@ -32131,7 +32169,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $609万
@@ -32140,13 +32178,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $910万
@@ -32154,7 +32192,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $739万
@@ -32162,7 +32200,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $901万
@@ -32170,15 +32208,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,105万
+$1105万
 $19,699/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $550万
@@ -32186,7 +32224,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $698万
@@ -32195,13 +32233,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $910万
@@ -32209,7 +32247,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $739万
@@ -32217,7 +32255,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $786万
@@ -32225,15 +32263,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,049万
+$1049万
 $18,697/呎
 (22年-07月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $550万
@@ -32241,7 +32279,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $640万
@@ -32250,13 +32288,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $860万
@@ -32264,7 +32302,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $736万
@@ -32272,7 +32310,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $898万
@@ -32280,15 +32318,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,093万
+$1093万
 $19,484/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $544万
@@ -32296,7 +32334,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $727万
@@ -32305,13 +32343,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $904万
@@ -32319,7 +32357,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $697万
@@ -32327,7 +32365,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $773万
@@ -32335,15 +32373,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,082万
+$1082万
 $19,282/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $542万
@@ -32351,7 +32389,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $688万
@@ -32360,13 +32398,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $857万
@@ -32374,7 +32412,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $571万
@@ -32382,7 +32420,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $772万
@@ -32390,15 +32428,15 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,078万
+$1078万
 $19,224/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $541万
@@ -32406,7 +32444,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $629万
@@ -32415,13 +32453,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $855万
@@ -32429,7 +32467,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $732万
@@ -32437,7 +32475,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $888万
@@ -32445,15 +32483,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,021万
+$1021万
 $18,191/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $758万
@@ -32461,7 +32499,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $720万
@@ -32470,13 +32508,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $868万
@@ -32484,7 +32522,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $693万
@@ -32492,7 +32530,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $841万
@@ -32500,15 +32538,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,072万
+$1072万
 $19,109/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $722万
@@ -32516,7 +32554,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $715万
@@ -32525,13 +32563,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $897万
@@ -32539,7 +32577,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $692万
@@ -32547,7 +32585,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $884万
@@ -32555,15 +32593,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,069万
+$1069万
 $19,050/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $720万
@@ -32571,7 +32609,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $565万
@@ -32580,13 +32618,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $895万
@@ -32594,7 +32632,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $690万
@@ -32602,7 +32640,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $883万
@@ -32610,15 +32648,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,011万
+$1011万
 $18,028/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $717万
@@ -32626,7 +32664,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $564万
@@ -32635,13 +32673,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $768万
@@ -32649,7 +32687,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $726万
@@ -32657,7 +32695,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $836万
@@ -32665,15 +32703,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,062万
+$1062万
 $18,938/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $715万
@@ -32681,7 +32719,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $708万
@@ -32690,13 +32728,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $893万
@@ -32704,7 +32742,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $689万
@@ -32712,7 +32750,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $881万
@@ -32720,15 +32758,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,008万
+$1008万
 $17,975/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $715万
@@ -32736,7 +32774,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $562万
@@ -32745,13 +32783,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $890万
@@ -32759,7 +32797,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $723万
@@ -32767,7 +32805,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $877万
@@ -32775,7 +32813,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $970万
@@ -32783,7 +32821,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $707万
@@ -32791,7 +32829,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $700万
@@ -32800,13 +32838,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $858万
@@ -32814,7 +32852,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $697万
@@ -32822,7 +32860,7 @@
 (22年-07月)</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $831万
@@ -32830,15 +32868,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,048万
+$1048万
 $18,675/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $669万
@@ -32846,7 +32884,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $663万
@@ -32855,13 +32893,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $874万
@@ -32869,7 +32907,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $566万
@@ -32877,7 +32915,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $566万
@@ -32885,15 +32923,15 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,045万
+$1045万
 $18,621/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $703万
@@ -32901,7 +32939,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $661万
@@ -32910,13 +32948,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $760万
@@ -32924,7 +32962,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $565万
@@ -32932,7 +32970,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $843万
@@ -32940,7 +32978,7 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $993万
@@ -32948,7 +32986,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $701万
@@ -32956,7 +32994,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G39" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $694万
@@ -32965,13 +33003,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $838万
@@ -32979,7 +33017,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $717万
@@ -32987,7 +33025,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $841万
@@ -32995,15 +33033,15 @@
 (22年-06月)</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E40" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,038万
+$1038万
 $18,508/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $699万
@@ -33011,7 +33049,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $692万
@@ -33020,13 +33058,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $881万
@@ -33034,7 +33072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $679万
@@ -33042,7 +33080,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D41" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $869万
@@ -33050,7 +33088,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $978万
@@ -33058,7 +33096,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $628万
@@ -33066,7 +33104,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G41" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $553万
@@ -33075,13 +33113,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $879万
@@ -33089,7 +33127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $714万
@@ -33097,7 +33135,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D42" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $867万
@@ -33105,15 +33143,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E42" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,027万
+$1027万
 $18,307/呎
 (22年-06月)</t>
         </is>
       </c>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $659万
@@ -33121,7 +33159,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="G42" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $665万
@@ -33130,13 +33168,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $878万
@@ -33144,7 +33182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $563万
@@ -33152,7 +33190,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $821万
@@ -33160,7 +33198,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E43" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $972万
@@ -33168,7 +33206,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="F43" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $693万
@@ -33176,7 +33214,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $686万
@@ -33185,13 +33223,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="65" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $878万
@@ -33199,7 +33237,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $713万
@@ -33207,7 +33245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D44" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $865万
@@ -33215,7 +33253,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E44" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $972万
@@ -33223,7 +33261,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F44" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $693万
@@ -33231,7 +33269,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $550万
@@ -33240,13 +33278,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="65" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
+    <row r="45" ht="58" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $874万
@@ -33254,7 +33292,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $710万
@@ -33262,7 +33300,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $818万
@@ -33270,7 +33308,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E45" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $966万
@@ -33278,7 +33316,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F45" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $689万
@@ -33286,7 +33324,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $682万
@@ -33295,13 +33333,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
+    <row r="46" ht="58" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $872万
@@ -33309,7 +33347,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $709万
@@ -33317,7 +33355,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D46" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $816万
@@ -33325,7 +33363,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E46" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $950万
@@ -33333,7 +33371,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F47" s="16" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $687万
@@ -33341,7 +33379,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $657万
@@ -33350,13 +33388,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="65" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
+    <row r="47" ht="58" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $748万
@@ -33364,7 +33402,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $707万
@@ -33372,7 +33410,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D47" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $858万
@@ -33380,15 +33418,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E47" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,039万
+$1039万
 $18,515/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="F47" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $685万
@@ -33396,7 +33434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $543万
@@ -33405,13 +33443,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
+    <row r="48" ht="58" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>A | 462呎 (2房)
 $825万
@@ -33419,7 +33457,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>B | 336呎 (1房)
 $560万
@@ -33427,7 +33465,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $857万
@@ -33435,15 +33473,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
-$1,068万
+$1068万
 $19,037/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $615万
@@ -33451,7 +33489,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $641万
@@ -33460,13 +33498,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="65" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>A | 461呎 (2房)
 $744万
@@ -33474,7 +33512,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>B | 335呎 (1房)
 $703万
@@ -33482,7 +33520,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D49" s="20" t="inlineStr">
         <is>
           <t>C | 461呎 (2房)
 $810万
@@ -33490,7 +33528,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>D | 561呎 (2房)
 $952万
@@ -33498,7 +33536,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>E | 337呎 (1房)
 $678万
@@ -33506,7 +33544,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G49" s="20" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
 $672万
@@ -33515,13 +33553,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="65" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
+    <row r="50" ht="58" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>A | 424呎 (2房)
 $758万
@@ -33529,7 +33567,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>B | 298呎 (1房)
 $527万
@@ -33537,7 +33575,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D50" s="20" t="inlineStr">
         <is>
           <t>C | 423呎 (2房)
 $742万
@@ -33545,7 +33583,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>D | 524呎 (2房)
 $958万
@@ -33553,7 +33591,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $540万
@@ -33561,7 +33599,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>F | 299呎 (1房)
 $543万
@@ -33572,7 +33610,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
